--- a/내편의_프로젝트/내편의_작업계획표_2026-11-20.xlsx
+++ b/내편의_프로젝트/내편의_작업계획표_2026-11-20.xlsx
@@ -5,23 +5,25 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HOME\내편의_프로젝트\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\2nd Project\내편의_프로젝트\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F16DE0-E3FF-4927-91B1-058A7F38E002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA38817D-0812-4511-9D39-88A07B339C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38220" yWindow="5235" windowWidth="16560" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="작업 계획" sheetId="1" r:id="rId1"/>
-    <sheet name="범위·결정" sheetId="2" r:id="rId2"/>
+    <sheet name="간트차트" sheetId="3" r:id="rId2"/>
+    <sheet name="역할분담표" sheetId="4" r:id="rId3"/>
+    <sheet name="범위·결정" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="205">
   <si>
     <t>내편의 프로젝트 | 11월 18일 완료 · 11월 20일 발표</t>
   </si>
@@ -510,6 +512,391 @@
   </si>
   <si>
     <t>계정 도입 시 보안·개인정보 설계 필요</t>
+  </si>
+  <si>
+    <t>기간</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>구분</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로젝트 기획</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>모델</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>UX/UI</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>포트폴리오 web</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>내편의 App</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>발표</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>문제 정의·서비스 방향</t>
+  </si>
+  <si>
+    <t>시각화·인사이트 정리</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결과</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>서비스</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적용</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>IA·사용자 흐름·와이어프레임</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>화면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>프런트엔드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>구현</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 기획·디자인·개발</t>
+  </si>
+  <si>
+    <t>PPT 디자인·대본 구성</t>
+  </si>
+  <si>
+    <t>10/27~10/29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">최종 발표           </t>
+  </si>
+  <si>
+    <t>10/30~11/1</t>
+  </si>
+  <si>
+    <t>11/2~11/5</t>
+  </si>
+  <si>
+    <t>11/6~11/8</t>
+  </si>
+  <si>
+    <t>11/9~11/11</t>
+  </si>
+  <si>
+    <t>11/12~11/14</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>11/15</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>■</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>■■■</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■■■</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>■■■■■</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>■■■■■■■</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>■■■■■■</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>11/16</t>
+  </si>
+  <si>
+    <t>11/17</t>
+  </si>
+  <si>
+    <t>11/18</t>
+  </si>
+  <si>
+    <t>11/19</t>
+  </si>
+  <si>
+    <t>포트폴리오 웹사이트</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>PPT·대본·발표 준비</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>위치 API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="210 M고딕OTF 030"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지하철 데이터 연동</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>백엔드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="210 M고딕OTF 030"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>데이터베이스 구축</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="210 M고딕OTF 030"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>API 구조 설계</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>요구사항</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="210 M고딕OTF 030"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>와이어프레임</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>프런트엔드</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="210 M고딕OTF 030"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>백엔드 연결</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>기능 구현</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t>·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="210 M고딕OTF 030"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>통합 테스트</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -519,7 +906,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -563,6 +950,64 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="210 M고딕OTF 030"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="210 M고딕OTF 030"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="210 M고딕OTF 030"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -577,7 +1022,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -585,12 +1030,236 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -639,6 +1308,75 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="14" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1704,6 +2442,299 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5060ABDB-7A45-4E48-BCD6-90AD6BFC797D}">
+  <dimension ref="A1:L10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="29.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1796875" customWidth="1"/>
+    <col min="8" max="12" width="6.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="19" customFormat="1" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="27" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="E1" s="29" t="s">
+        <v>183</v>
+      </c>
+      <c r="F1" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="G1" s="29" t="s">
+        <v>185</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>193</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="L1" s="31" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="C2" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="D2" s="33"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="35"/>
+    </row>
+    <row r="3" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="B3" s="36"/>
+      <c r="C3" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="37"/>
+    </row>
+    <row r="4" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="B4" s="36"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="38" t="s">
+        <v>191</v>
+      </c>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="37"/>
+    </row>
+    <row r="5" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="37"/>
+    </row>
+    <row r="6" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="36"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="37"/>
+    </row>
+    <row r="7" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="36"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="37"/>
+    </row>
+    <row r="8" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="36"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="37"/>
+    </row>
+    <row r="9" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="36"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="37"/>
+    </row>
+    <row r="10" spans="1:12" ht="22" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="25" t="s">
+        <v>180</v>
+      </c>
+      <c r="B10" s="40"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="42" t="s">
+        <v>187</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB5EBF80-600F-4EDB-9D6B-F9CE7A43946F}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="21"/>
+    </row>
+    <row r="2" spans="1:2" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>178</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF52789B"/>
